--- a/datos/Modelo_de_Carrito.xlsx
+++ b/datos/Modelo_de_Carrito.xlsx
@@ -462,7 +462,7 @@
         <v>25787.04</v>
       </c>
       <c r="J2">
-        <v>11030</v>
+        <v>14307</v>
       </c>
       <c r="K2">
         <v>9999999</v>
@@ -518,7 +518,7 @@
         <v>25787.04</v>
       </c>
       <c r="J3">
-        <v>16977</v>
+        <v>32901</v>
       </c>
       <c r="K3">
         <v>9999999</v>
@@ -574,7 +574,7 @@
         <v>13672.81</v>
       </c>
       <c r="J4">
-        <v>102063</v>
+        <v>243918</v>
       </c>
       <c r="K4">
         <v>9999999</v>
@@ -630,7 +630,7 @@
         <v>25787.04</v>
       </c>
       <c r="J5">
-        <v>215138</v>
+        <v>197805</v>
       </c>
       <c r="K5">
         <v>9999999</v>
@@ -686,7 +686,7 @@
         <v>28177.94</v>
       </c>
       <c r="J6">
-        <v>15711</v>
+        <v>13290</v>
       </c>
       <c r="K6">
         <v>9999999</v>
@@ -742,7 +742,7 @@
         <v>25787.04</v>
       </c>
       <c r="J7">
-        <v>27258</v>
+        <v>36763</v>
       </c>
       <c r="K7">
         <v>9999999</v>
@@ -854,7 +854,7 @@
         <v>30159.11</v>
       </c>
       <c r="J9">
-        <v>28466</v>
+        <v>22781</v>
       </c>
       <c r="K9">
         <v>9999999</v>
@@ -910,7 +910,7 @@
         <v>25787.04</v>
       </c>
       <c r="J10">
-        <v>17958</v>
+        <v>18932</v>
       </c>
       <c r="K10">
         <v>9999999</v>
@@ -966,7 +966,7 @@
         <v>25787.04</v>
       </c>
       <c r="J11">
-        <v>13459</v>
+        <v>10326</v>
       </c>
       <c r="K11">
         <v>9999999</v>
@@ -1022,7 +1022,7 @@
         <v>25787.04</v>
       </c>
       <c r="J12">
-        <v>11835</v>
+        <v>25338</v>
       </c>
       <c r="K12">
         <v>9999999</v>
@@ -1078,7 +1078,7 @@
         <v>25787.04</v>
       </c>
       <c r="J13">
-        <v>18913</v>
+        <v>16740</v>
       </c>
       <c r="K13">
         <v>9999999</v>
@@ -1134,7 +1134,7 @@
         <v>28177.94</v>
       </c>
       <c r="J14">
-        <v>13434</v>
+        <v>17726</v>
       </c>
       <c r="K14">
         <v>9999999</v>
@@ -1190,7 +1190,7 @@
         <v>30159.11</v>
       </c>
       <c r="J15">
-        <v>8083</v>
+        <v>8514</v>
       </c>
       <c r="K15">
         <v>9999999</v>
@@ -1246,7 +1246,7 @@
         <v>16178.93</v>
       </c>
       <c r="J16">
-        <v>15694</v>
+        <v>22498</v>
       </c>
       <c r="K16">
         <v>9999999</v>
@@ -1302,7 +1302,7 @@
         <v>30159.11</v>
       </c>
       <c r="J17">
-        <v>19028</v>
+        <v>16172</v>
       </c>
       <c r="K17">
         <v>9999999</v>
@@ -1358,7 +1358,7 @@
         <v>28177.94</v>
       </c>
       <c r="J18">
-        <v>10885</v>
+        <v>9288</v>
       </c>
       <c r="K18">
         <v>9999999</v>
@@ -1414,7 +1414,7 @@
         <v>28177.94</v>
       </c>
       <c r="J19">
-        <v>6425</v>
+        <v>15797</v>
       </c>
       <c r="K19">
         <v>9999999</v>
@@ -1467,10 +1467,10 @@
         <v>0</v>
       </c>
       <c r="I20">
-        <v>26783.85</v>
+        <v>27319.53</v>
       </c>
       <c r="J20">
-        <v>87462</v>
+        <v>51189</v>
       </c>
       <c r="K20">
         <v>9999999</v>
@@ -1526,7 +1526,7 @@
         <v>28177.94</v>
       </c>
       <c r="J21">
-        <v>6284</v>
+        <v>8594</v>
       </c>
       <c r="K21">
         <v>9999999</v>
@@ -1582,7 +1582,7 @@
         <v>28177.94</v>
       </c>
       <c r="J22">
-        <v>11913</v>
+        <v>7677</v>
       </c>
       <c r="K22">
         <v>9999999</v>
@@ -1638,7 +1638,7 @@
         <v>25787.04</v>
       </c>
       <c r="J23">
-        <v>16842</v>
+        <v>29355</v>
       </c>
       <c r="K23">
         <v>9999999</v>
@@ -1694,7 +1694,7 @@
         <v>30159.11</v>
       </c>
       <c r="J24">
-        <v>7089</v>
+        <v>6945</v>
       </c>
       <c r="K24">
         <v>9999999</v>
@@ -1750,7 +1750,7 @@
         <v>15060.35</v>
       </c>
       <c r="J25">
-        <v>12982</v>
+        <v>10154</v>
       </c>
       <c r="K25">
         <v>9999999</v>
@@ -1806,7 +1806,7 @@
         <v>28177.94</v>
       </c>
       <c r="J26">
-        <v>7945</v>
+        <v>7390</v>
       </c>
       <c r="K26">
         <v>9999999</v>
@@ -1859,10 +1859,10 @@
         <v>0</v>
       </c>
       <c r="I27">
-        <v>14416.92</v>
+        <v>14993.59</v>
       </c>
       <c r="J27">
-        <v>13199</v>
+        <v>3852</v>
       </c>
       <c r="K27">
         <v>9999999</v>
@@ -1918,7 +1918,7 @@
         <v>30159.11</v>
       </c>
       <c r="J28">
-        <v>2749</v>
+        <v>9668</v>
       </c>
       <c r="K28">
         <v>9999999</v>
@@ -1971,10 +1971,10 @@
         <v>0</v>
       </c>
       <c r="I29">
-        <v>14416.92</v>
+        <v>14993.59</v>
       </c>
       <c r="J29">
-        <v>26130</v>
+        <v>20465</v>
       </c>
       <c r="K29">
         <v>9999999</v>
@@ -2030,7 +2030,7 @@
         <v>14544.03</v>
       </c>
       <c r="J30">
-        <v>96571</v>
+        <v>86148</v>
       </c>
       <c r="K30">
         <v>9999999</v>
@@ -2083,10 +2083,10 @@
         <v>0</v>
       </c>
       <c r="I31">
-        <v>23882.61</v>
+        <v>24360.26</v>
       </c>
       <c r="J31">
-        <v>35652</v>
+        <v>22802</v>
       </c>
       <c r="K31">
         <v>9999999</v>
@@ -2139,10 +2139,10 @@
         <v>0</v>
       </c>
       <c r="I32">
-        <v>33763.54</v>
+        <v>34776.45</v>
       </c>
       <c r="J32">
-        <v>50874</v>
+        <v>94829</v>
       </c>
       <c r="K32">
         <v>9999999</v>
@@ -2198,7 +2198,7 @@
         <v>28177.94</v>
       </c>
       <c r="J33">
-        <v>9021</v>
+        <v>14932</v>
       </c>
       <c r="K33">
         <v>9999999</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="I34">
-        <v>14416.92</v>
+        <v>14993.59</v>
       </c>
       <c r="J34">
-        <v>28065</v>
+        <v>18352</v>
       </c>
       <c r="K34">
         <v>9999999</v>
@@ -2307,10 +2307,10 @@
         <v>0</v>
       </c>
       <c r="I35">
-        <v>14416.92</v>
+        <v>14993.59</v>
       </c>
       <c r="J35">
-        <v>22448</v>
+        <v>16165</v>
       </c>
       <c r="K35">
         <v>9999999</v>
@@ -2363,10 +2363,10 @@
         <v>0</v>
       </c>
       <c r="I36">
-        <v>33763.54</v>
+        <v>34776.45</v>
       </c>
       <c r="J36">
-        <v>127451</v>
+        <v>112505</v>
       </c>
       <c r="K36">
         <v>9999999</v>
@@ -2422,7 +2422,7 @@
         <v>10594.62</v>
       </c>
       <c r="J37">
-        <v>206918</v>
+        <v>200652</v>
       </c>
       <c r="K37">
         <v>9999999</v>
@@ -2475,10 +2475,10 @@
         <v>0</v>
       </c>
       <c r="I38">
-        <v>33763.54</v>
+        <v>34776.45</v>
       </c>
       <c r="J38">
-        <v>99117</v>
+        <v>89403</v>
       </c>
       <c r="K38">
         <v>9999999</v>
@@ -2587,10 +2587,10 @@
         <v>0</v>
       </c>
       <c r="I40">
-        <v>22635.94</v>
+        <v>23088.65</v>
       </c>
       <c r="J40">
-        <v>41942</v>
+        <v>36714</v>
       </c>
       <c r="K40">
         <v>9999999</v>
@@ -2646,7 +2646,7 @@
         <v>30159.11</v>
       </c>
       <c r="J41">
-        <v>21726</v>
+        <v>34746</v>
       </c>
       <c r="K41">
         <v>9999999</v>
@@ -2699,10 +2699,10 @@
         <v>0</v>
       </c>
       <c r="I42">
-        <v>14416.92</v>
+        <v>14993.59</v>
       </c>
       <c r="J42">
-        <v>11806</v>
+        <v>8046</v>
       </c>
       <c r="K42">
         <v>9999999</v>
@@ -2755,10 +2755,10 @@
         <v>0</v>
       </c>
       <c r="I43">
-        <v>14416.92</v>
+        <v>14993.59</v>
       </c>
       <c r="J43">
-        <v>22696</v>
+        <v>17366</v>
       </c>
       <c r="K43">
         <v>9999999</v>
@@ -2811,10 +2811,10 @@
         <v>0</v>
       </c>
       <c r="I44">
-        <v>14416.92</v>
+        <v>14993.59</v>
       </c>
       <c r="J44">
-        <v>80151</v>
+        <v>114087</v>
       </c>
       <c r="K44">
         <v>9999999</v>
@@ -2870,7 +2870,7 @@
         <v>28177.94</v>
       </c>
       <c r="J45">
-        <v>16306</v>
+        <v>16653</v>
       </c>
       <c r="K45">
         <v>9999999</v>
@@ -2923,10 +2923,10 @@
         <v>0</v>
       </c>
       <c r="I46">
-        <v>14416.92</v>
+        <v>14993.59</v>
       </c>
       <c r="J46">
-        <v>85430</v>
+        <v>77523</v>
       </c>
       <c r="K46">
         <v>9999999</v>
@@ -2982,7 +2982,7 @@
         <v>25787.04</v>
       </c>
       <c r="J47">
-        <v>97696</v>
+        <v>94450</v>
       </c>
       <c r="K47">
         <v>9999999</v>
@@ -3038,7 +3038,7 @@
         <v>10594.62</v>
       </c>
       <c r="J48">
-        <v>37067</v>
+        <v>33287</v>
       </c>
       <c r="K48">
         <v>9999999</v>
@@ -3094,7 +3094,7 @@
         <v>12822.77</v>
       </c>
       <c r="J49">
-        <v>21656</v>
+        <v>9325</v>
       </c>
       <c r="K49">
         <v>9999999</v>
@@ -3150,7 +3150,7 @@
         <v>13672.81</v>
       </c>
       <c r="J50">
-        <v>4444</v>
+        <v>6817</v>
       </c>
       <c r="K50">
         <v>9999999</v>
@@ -3206,7 +3206,7 @@
         <v>12822.77</v>
       </c>
       <c r="J51">
-        <v>15448</v>
+        <v>20868</v>
       </c>
       <c r="K51">
         <v>9999999</v>
@@ -3259,10 +3259,10 @@
         <v>0</v>
       </c>
       <c r="I52">
-        <v>14416.92</v>
+        <v>14993.59</v>
       </c>
       <c r="J52">
-        <v>20296</v>
+        <v>18629</v>
       </c>
       <c r="K52">
         <v>9999999</v>
@@ -3315,10 +3315,10 @@
         <v>0</v>
       </c>
       <c r="I53">
-        <v>33763.54</v>
+        <v>34776.45</v>
       </c>
       <c r="J53">
-        <v>16340</v>
+        <v>49102</v>
       </c>
       <c r="K53">
         <v>9999999</v>
@@ -3374,7 +3374,7 @@
         <v>13672.81</v>
       </c>
       <c r="J54">
-        <v>10995</v>
+        <v>9444</v>
       </c>
       <c r="K54">
         <v>9999999</v>
@@ -3430,7 +3430,7 @@
         <v>13672.81</v>
       </c>
       <c r="J55">
-        <v>37951</v>
+        <v>35842</v>
       </c>
       <c r="K55">
         <v>9999999</v>
@@ -3486,7 +3486,7 @@
         <v>25787.04</v>
       </c>
       <c r="J56">
-        <v>46365</v>
+        <v>57509</v>
       </c>
       <c r="K56">
         <v>9999999</v>
@@ -3542,7 +3542,7 @@
         <v>25787.04</v>
       </c>
       <c r="J57">
-        <v>32066</v>
+        <v>36739</v>
       </c>
       <c r="K57">
         <v>9999999</v>
@@ -3598,7 +3598,7 @@
         <v>25787.04</v>
       </c>
       <c r="J58">
-        <v>35432</v>
+        <v>45785</v>
       </c>
       <c r="K58">
         <v>9999999</v>
@@ -3654,7 +3654,7 @@
         <v>30159.11</v>
       </c>
       <c r="J59">
-        <v>13706</v>
+        <v>19908</v>
       </c>
       <c r="K59">
         <v>9999999</v>
@@ -3707,10 +3707,10 @@
         <v>0</v>
       </c>
       <c r="I60">
-        <v>14416.92</v>
+        <v>14993.59</v>
       </c>
       <c r="J60">
-        <v>32900</v>
+        <v>27111</v>
       </c>
       <c r="K60">
         <v>9999999</v>
@@ -3763,10 +3763,10 @@
         <v>0</v>
       </c>
       <c r="I61">
-        <v>14416.92</v>
+        <v>14993.59</v>
       </c>
       <c r="J61">
-        <v>6207</v>
+        <v>2952</v>
       </c>
       <c r="K61">
         <v>9999999</v>
@@ -3819,10 +3819,10 @@
         <v>0</v>
       </c>
       <c r="I62">
-        <v>29165.86</v>
+        <v>31207.47</v>
       </c>
       <c r="J62">
-        <v>30646</v>
+        <v>23970</v>
       </c>
       <c r="K62">
         <v>9999999</v>
@@ -3875,10 +3875,10 @@
         <v>0</v>
       </c>
       <c r="I63">
-        <v>14416.92</v>
+        <v>14993.59</v>
       </c>
       <c r="J63">
-        <v>19193</v>
+        <v>13616</v>
       </c>
       <c r="K63">
         <v>9999999</v>
@@ -3987,10 +3987,10 @@
         <v>0</v>
       </c>
       <c r="I65">
-        <v>63642.1</v>
+        <v>70515.5</v>
       </c>
       <c r="J65">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="K65">
         <v>9999999</v>
@@ -4043,10 +4043,10 @@
         <v>0</v>
       </c>
       <c r="I66">
-        <v>61062.9</v>
+        <v>67657.7</v>
       </c>
       <c r="J66">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="K66">
         <v>9999999</v>
@@ -4099,10 +4099,10 @@
         <v>0</v>
       </c>
       <c r="I67">
-        <v>78005.8</v>
+        <v>86430.4</v>
       </c>
       <c r="J67">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="K67">
         <v>9999999</v>
@@ -4214,7 +4214,7 @@
         <v>30159.11</v>
       </c>
       <c r="J69">
-        <v>20578</v>
+        <v>38088</v>
       </c>
       <c r="K69">
         <v>9999999</v>
@@ -4267,10 +4267,10 @@
         <v>0</v>
       </c>
       <c r="I70">
-        <v>25468.4</v>
+        <v>27509.6</v>
       </c>
       <c r="J70">
-        <v>1479</v>
+        <v>1426</v>
       </c>
       <c r="K70">
         <v>9999999</v>
@@ -4323,10 +4323,10 @@
         <v>0</v>
       </c>
       <c r="I71">
-        <v>39742.78</v>
+        <v>41245.87</v>
       </c>
       <c r="J71">
-        <v>1481</v>
+        <v>853</v>
       </c>
       <c r="K71">
         <v>9999999</v>
@@ -4379,10 +4379,10 @@
         <v>0</v>
       </c>
       <c r="I72">
-        <v>37847.7</v>
+        <v>42514.09</v>
       </c>
       <c r="J72">
-        <v>372</v>
+        <v>597</v>
       </c>
       <c r="K72">
         <v>9999999</v>
@@ -4435,10 +4435,10 @@
         <v>0</v>
       </c>
       <c r="I73">
-        <v>29165.86</v>
+        <v>31207.47</v>
       </c>
       <c r="J73">
-        <v>11182</v>
+        <v>20515</v>
       </c>
       <c r="K73">
         <v>9999999</v>
@@ -4491,10 +4491,10 @@
         <v>0</v>
       </c>
       <c r="I74">
-        <v>29165.86</v>
+        <v>31207.47</v>
       </c>
       <c r="J74">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K74">
         <v>9999999</v>
@@ -4550,7 +4550,7 @@
         <v>82471.5</v>
       </c>
       <c r="J75">
-        <v>305</v>
+        <v>425</v>
       </c>
       <c r="K75">
         <v>9999999</v>
@@ -4603,10 +4603,10 @@
         <v>0</v>
       </c>
       <c r="I76">
-        <v>16736.9</v>
+        <v>16798.76</v>
       </c>
       <c r="J76">
-        <v>1044</v>
+        <v>1017</v>
       </c>
       <c r="K76">
         <v>9999999</v>
@@ -4659,10 +4659,10 @@
         <v>0</v>
       </c>
       <c r="I77">
-        <v>16736.9</v>
+        <v>16798.76</v>
       </c>
       <c r="J77">
-        <v>2677</v>
+        <v>1754</v>
       </c>
       <c r="K77">
         <v>9999999</v>
@@ -4715,10 +4715,10 @@
         <v>0</v>
       </c>
       <c r="I78">
-        <v>16736.9</v>
+        <v>16798.76</v>
       </c>
       <c r="J78">
-        <v>2877</v>
+        <v>3322</v>
       </c>
       <c r="K78">
         <v>9999999</v>
@@ -4771,7 +4771,7 @@
         <v>0</v>
       </c>
       <c r="I79">
-        <v>16736.9</v>
+        <v>16798.76</v>
       </c>
       <c r="J79">
         <v>0</v>
@@ -4827,7 +4827,7 @@
         <v>0</v>
       </c>
       <c r="I80">
-        <v>16736.9</v>
+        <v>16798.76</v>
       </c>
       <c r="J80">
         <v>0</v>
@@ -4883,10 +4883,10 @@
         <v>0</v>
       </c>
       <c r="I81">
-        <v>16736.9</v>
+        <v>16798.76</v>
       </c>
       <c r="J81">
-        <v>1317</v>
+        <v>296</v>
       </c>
       <c r="K81">
         <v>9999999</v>
@@ -4939,10 +4939,10 @@
         <v>0</v>
       </c>
       <c r="I82">
-        <v>16736.9</v>
+        <v>16798.76</v>
       </c>
       <c r="J82">
-        <v>0</v>
+        <v>990</v>
       </c>
       <c r="K82">
         <v>9999999</v>
@@ -4995,10 +4995,10 @@
         <v>0</v>
       </c>
       <c r="I83">
-        <v>16736.9</v>
+        <v>16798.76</v>
       </c>
       <c r="J83">
-        <v>0</v>
+        <v>931</v>
       </c>
       <c r="K83">
         <v>9999999</v>
@@ -5051,10 +5051,10 @@
         <v>0</v>
       </c>
       <c r="I84">
-        <v>16736.9</v>
+        <v>16798.76</v>
       </c>
       <c r="J84">
-        <v>0</v>
+        <v>273</v>
       </c>
       <c r="K84">
         <v>9999999</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="I85">
-        <v>27100.8</v>
+        <v>27642.82</v>
       </c>
       <c r="J85">
-        <v>149989</v>
+        <v>135303</v>
       </c>
       <c r="K85">
         <v>9999999</v>
@@ -5166,7 +5166,7 @@
         <v>13243.28</v>
       </c>
       <c r="J86">
-        <v>4435</v>
+        <v>0</v>
       </c>
       <c r="K86">
         <v>9999999</v>
@@ -5219,10 +5219,10 @@
         <v>0</v>
       </c>
       <c r="I87">
-        <v>40055.57</v>
+        <v>41556.99</v>
       </c>
       <c r="J87">
-        <v>1777</v>
+        <v>0</v>
       </c>
       <c r="K87">
         <v>9999999</v>
@@ -5331,10 +5331,10 @@
         <v>0</v>
       </c>
       <c r="I89">
-        <v>49219.68</v>
+        <v>51105.86</v>
       </c>
       <c r="J89">
-        <v>1627</v>
+        <v>3133</v>
       </c>
       <c r="K89">
         <v>9999999</v>
@@ -5387,10 +5387,10 @@
         <v>0</v>
       </c>
       <c r="I90">
-        <v>44098.94</v>
+        <v>46058.56</v>
       </c>
       <c r="J90">
-        <v>1979</v>
+        <v>3007</v>
       </c>
       <c r="K90">
         <v>9999999</v>
@@ -5443,10 +5443,10 @@
         <v>0</v>
       </c>
       <c r="I91">
-        <v>31987.38</v>
+        <v>33174.96</v>
       </c>
       <c r="J91">
-        <v>375</v>
+        <v>867</v>
       </c>
       <c r="K91">
         <v>9999999</v>
@@ -5499,10 +5499,10 @@
         <v>0</v>
       </c>
       <c r="I92">
-        <v>40463.06</v>
+        <v>41933.33</v>
       </c>
       <c r="J92">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="K92">
         <v>9999999</v>
@@ -5555,10 +5555,10 @@
         <v>0</v>
       </c>
       <c r="I93">
-        <v>36088.57</v>
+        <v>37462.26</v>
       </c>
       <c r="J93">
-        <v>0</v>
+        <v>690</v>
       </c>
       <c r="K93">
         <v>9999999</v>
@@ -5611,10 +5611,10 @@
         <v>0</v>
       </c>
       <c r="I94">
-        <v>39880.54</v>
+        <v>41492.38</v>
       </c>
       <c r="J94">
-        <v>2000</v>
+        <v>1988</v>
       </c>
       <c r="K94">
         <v>9999999</v>
@@ -5667,10 +5667,10 @@
         <v>0</v>
       </c>
       <c r="I95">
-        <v>76702.56</v>
+        <v>77326.16</v>
       </c>
       <c r="J95">
-        <v>11988</v>
+        <v>21034</v>
       </c>
       <c r="K95">
         <v>9999999</v>
@@ -5723,10 +5723,10 @@
         <v>0</v>
       </c>
       <c r="I96">
-        <v>76702.56</v>
+        <v>77326.16</v>
       </c>
       <c r="J96">
-        <v>14505</v>
+        <v>15678</v>
       </c>
       <c r="K96">
         <v>9999999</v>
@@ -5782,7 +5782,7 @@
         <v>18825.43</v>
       </c>
       <c r="J97">
-        <v>18977</v>
+        <v>14673</v>
       </c>
       <c r="K97">
         <v>9999999</v>
@@ -5838,7 +5838,7 @@
         <v>77008.37</v>
       </c>
       <c r="J98">
-        <v>4011</v>
+        <v>3518</v>
       </c>
       <c r="K98">
         <v>9999999</v>
@@ -5894,7 +5894,7 @@
         <v>77008.37</v>
       </c>
       <c r="J99">
-        <v>3135</v>
+        <v>2646</v>
       </c>
       <c r="K99">
         <v>9999999</v>
@@ -5950,7 +5950,7 @@
         <v>18825.43</v>
       </c>
       <c r="J100">
-        <v>78203</v>
+        <v>72950</v>
       </c>
       <c r="K100">
         <v>9999999</v>
@@ -6006,7 +6006,7 @@
         <v>32092</v>
       </c>
       <c r="J101">
-        <v>19023</v>
+        <v>22550</v>
       </c>
       <c r="K101">
         <v>9999999</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="I102">
-        <v>24877.72</v>
+        <v>25375.28</v>
       </c>
       <c r="J102">
-        <v>0</v>
+        <v>18006</v>
       </c>
       <c r="K102">
         <v>9999999</v>
@@ -6115,10 +6115,10 @@
         <v>0</v>
       </c>
       <c r="I103">
-        <v>29165.86</v>
+        <v>31207.47</v>
       </c>
       <c r="J103">
-        <v>23854</v>
+        <v>38991</v>
       </c>
       <c r="K103">
         <v>9999999</v>
@@ -6174,7 +6174,7 @@
         <v>13243.28</v>
       </c>
       <c r="J104">
-        <v>13596</v>
+        <v>8389</v>
       </c>
       <c r="K104">
         <v>9999999</v>
@@ -6230,7 +6230,7 @@
         <v>30159.11</v>
       </c>
       <c r="J105">
-        <v>11075</v>
+        <v>480</v>
       </c>
       <c r="K105">
         <v>9999999</v>
@@ -6342,7 +6342,7 @@
         <v>13672.81</v>
       </c>
       <c r="J107">
-        <v>4696</v>
+        <v>11330</v>
       </c>
       <c r="K107">
         <v>9999999</v>
@@ -6395,10 +6395,10 @@
         <v>0</v>
       </c>
       <c r="I108">
-        <v>25468.4</v>
+        <v>27509.6</v>
       </c>
       <c r="J108">
-        <v>2966</v>
+        <v>2899</v>
       </c>
       <c r="K108">
         <v>9999999</v>
@@ -6451,10 +6451,10 @@
         <v>0</v>
       </c>
       <c r="I109">
-        <v>25468.4</v>
+        <v>27509.6</v>
       </c>
       <c r="J109">
-        <v>2395</v>
+        <v>2296</v>
       </c>
       <c r="K109">
         <v>9999999</v>
@@ -6507,10 +6507,10 @@
         <v>0</v>
       </c>
       <c r="I110">
-        <v>25468.4</v>
+        <v>27509.6</v>
       </c>
       <c r="J110">
-        <v>1661</v>
+        <v>1569</v>
       </c>
       <c r="K110">
         <v>9999999</v>
@@ -6563,10 +6563,10 @@
         <v>0</v>
       </c>
       <c r="I111">
-        <v>25468.4</v>
+        <v>27509.6</v>
       </c>
       <c r="J111">
-        <v>2511</v>
+        <v>2408</v>
       </c>
       <c r="K111">
         <v>9999999</v>
@@ -6622,7 +6622,7 @@
         <v>30159.11</v>
       </c>
       <c r="J112">
-        <v>16651</v>
+        <v>10701</v>
       </c>
       <c r="K112">
         <v>9999999</v>
@@ -6678,7 +6678,7 @@
         <v>53452.9</v>
       </c>
       <c r="J113">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K113">
         <v>9999999</v>
@@ -6731,10 +6731,10 @@
         <v>0</v>
       </c>
       <c r="I114">
-        <v>36194.8</v>
+        <v>40103.8</v>
       </c>
       <c r="J114">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="K114">
         <v>9999999</v>
@@ -6787,10 +6787,10 @@
         <v>0</v>
       </c>
       <c r="I115">
-        <v>23569.7</v>
+        <v>26115.2</v>
       </c>
       <c r="J115">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="K115">
         <v>9999999</v>
@@ -6843,10 +6843,10 @@
         <v>0</v>
       </c>
       <c r="I116">
-        <v>24491.8</v>
+        <v>27143</v>
       </c>
       <c r="J116">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="K116">
         <v>9999999</v>
@@ -6899,10 +6899,10 @@
         <v>0</v>
       </c>
       <c r="I117">
-        <v>36803</v>
+        <v>40777.7</v>
       </c>
       <c r="J117">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K117">
         <v>9999999</v>
@@ -7179,10 +7179,10 @@
         <v>0</v>
       </c>
       <c r="I122">
-        <v>58637.5</v>
+        <v>64970.4</v>
       </c>
       <c r="J122">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="K122">
         <v>9999999</v>
@@ -7238,7 +7238,7 @@
         <v>90331.2</v>
       </c>
       <c r="J123">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="K123">
         <v>9999999</v>
@@ -7294,7 +7294,7 @@
         <v>4858.5</v>
       </c>
       <c r="J124">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K124">
         <v>9999999</v>
@@ -7350,7 +7350,7 @@
         <v>11362.3</v>
       </c>
       <c r="J125">
-        <v>163</v>
+        <v>51</v>
       </c>
       <c r="K125">
         <v>9999999</v>
@@ -7403,10 +7403,10 @@
         <v>0</v>
       </c>
       <c r="I126">
-        <v>31242</v>
+        <v>36654</v>
       </c>
       <c r="J126">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="K126">
         <v>9999999</v>
@@ -7462,7 +7462,7 @@
         <v>6117</v>
       </c>
       <c r="J127">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="K127">
         <v>9999999</v>
@@ -7518,7 +7518,7 @@
         <v>45395.8</v>
       </c>
       <c r="J128">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K128">
         <v>9999999</v>
@@ -7571,10 +7571,10 @@
         <v>0</v>
       </c>
       <c r="I129">
-        <v>5695.5</v>
+        <v>8487</v>
       </c>
       <c r="J129">
-        <v>0</v>
+        <v>2169</v>
       </c>
       <c r="K129">
         <v>9999999</v>
@@ -7686,7 +7686,7 @@
         <v>5783</v>
       </c>
       <c r="J131">
-        <v>1941</v>
+        <v>3475</v>
       </c>
       <c r="K131">
         <v>9999999</v>
@@ -7742,7 +7742,7 @@
         <v>7665.5</v>
       </c>
       <c r="J132">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K132">
         <v>9999999</v>
@@ -7798,7 +7798,7 @@
         <v>11278.9</v>
       </c>
       <c r="J133">
-        <v>212</v>
+        <v>150</v>
       </c>
       <c r="K133">
         <v>9999999</v>
@@ -7854,7 +7854,7 @@
         <v>6840</v>
       </c>
       <c r="J134">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="K134">
         <v>9999999</v>
@@ -7907,10 +7907,10 @@
         <v>0</v>
       </c>
       <c r="I135">
-        <v>1290.4</v>
+        <v>1414.5</v>
       </c>
       <c r="J135">
-        <v>425</v>
+        <v>262</v>
       </c>
       <c r="K135">
         <v>9999999</v>
@@ -7966,7 +7966,7 @@
         <v>3215.3</v>
       </c>
       <c r="J136">
-        <v>2145</v>
+        <v>1857</v>
       </c>
       <c r="K136">
         <v>9999999</v>
@@ -8246,7 +8246,7 @@
         <v>15498</v>
       </c>
       <c r="J141">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="K141">
         <v>9999999</v>
@@ -8299,10 +8299,10 @@
         <v>0</v>
       </c>
       <c r="I142">
-        <v>11778.5</v>
+        <v>12386.1</v>
       </c>
       <c r="J142">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="K142">
         <v>9999999</v>
@@ -8358,7 +8358,7 @@
         <v>10163.5</v>
       </c>
       <c r="J143">
-        <v>600</v>
+        <v>485</v>
       </c>
       <c r="K143">
         <v>9999999</v>
@@ -8470,7 +8470,7 @@
         <v>11426.7</v>
       </c>
       <c r="J145">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K145">
         <v>9999999</v>
@@ -8582,7 +8582,7 @@
         <v>195.9</v>
       </c>
       <c r="J147">
-        <v>169</v>
+        <v>140</v>
       </c>
       <c r="K147">
         <v>9999999</v>
@@ -8638,7 +8638,7 @@
         <v>25189.2</v>
       </c>
       <c r="J148">
-        <v>1051</v>
+        <v>840</v>
       </c>
       <c r="K148">
         <v>9999999</v>
@@ -8694,7 +8694,7 @@
         <v>142680</v>
       </c>
       <c r="J149">
-        <v>392</v>
+        <v>369</v>
       </c>
       <c r="K149">
         <v>9999999</v>
@@ -8803,10 +8803,10 @@
         <v>0</v>
       </c>
       <c r="I151">
-        <v>79335.4</v>
+        <v>86037.2</v>
       </c>
       <c r="J151">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K151">
         <v>9999999</v>
@@ -8862,7 +8862,7 @@
         <v>9014.5</v>
       </c>
       <c r="J152">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="K152">
         <v>9999999</v>
@@ -8918,7 +8918,7 @@
         <v>5452.6</v>
       </c>
       <c r="J153">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K153">
         <v>9999999</v>
@@ -9086,7 +9086,7 @@
         <v>45395.8</v>
       </c>
       <c r="J156">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="K156">
         <v>9999999</v>
@@ -9142,7 +9142,7 @@
         <v>13932.3</v>
       </c>
       <c r="J157">
-        <v>429</v>
+        <v>368</v>
       </c>
       <c r="K157">
         <v>9999999</v>
@@ -9198,7 +9198,7 @@
         <v>14231.5</v>
       </c>
       <c r="J158">
-        <v>316</v>
+        <v>214</v>
       </c>
       <c r="K158">
         <v>9999999</v>
@@ -9254,7 +9254,7 @@
         <v>2259.9</v>
       </c>
       <c r="J159">
-        <v>10632</v>
+        <v>9401</v>
       </c>
       <c r="K159">
         <v>9999999</v>
@@ -9307,10 +9307,10 @@
         <v>0</v>
       </c>
       <c r="I160">
-        <v>22885</v>
+        <v>26450</v>
       </c>
       <c r="J160">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="K160">
         <v>9999999</v>
@@ -9366,7 +9366,7 @@
         <v>27853.4</v>
       </c>
       <c r="J161">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="K161">
         <v>9999999</v>
@@ -9419,10 +9419,10 @@
         <v>0</v>
       </c>
       <c r="I162">
-        <v>39679.7</v>
+        <v>39699.8</v>
       </c>
       <c r="J162">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="K162">
         <v>9999999</v>
@@ -9475,10 +9475,10 @@
         <v>0</v>
       </c>
       <c r="I163">
-        <v>21480</v>
+        <v>27810</v>
       </c>
       <c r="J163">
-        <v>641</v>
+        <v>896</v>
       </c>
       <c r="K163">
         <v>9999999</v>
@@ -9534,7 +9534,7 @@
         <v>14112</v>
       </c>
       <c r="J164">
-        <v>10572</v>
+        <v>8443</v>
       </c>
       <c r="K164">
         <v>9999999</v>
@@ -9590,7 +9590,7 @@
         <v>40596</v>
       </c>
       <c r="J165">
-        <v>348</v>
+        <v>438</v>
       </c>
       <c r="K165">
         <v>9999999</v>
@@ -9646,7 +9646,7 @@
         <v>40596</v>
       </c>
       <c r="J166">
-        <v>691</v>
+        <v>398</v>
       </c>
       <c r="K166">
         <v>9999999</v>
@@ -9702,7 +9702,7 @@
         <v>225845.3</v>
       </c>
       <c r="J167">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K167">
         <v>9999999</v>
@@ -9811,10 +9811,10 @@
         <v>0</v>
       </c>
       <c r="I169">
-        <v>1734.3</v>
+        <v>1808.1</v>
       </c>
       <c r="J169">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="K169">
         <v>9999999</v>
@@ -9870,7 +9870,7 @@
         <v>15633.6</v>
       </c>
       <c r="J170">
-        <v>314</v>
+        <v>273</v>
       </c>
       <c r="K170">
         <v>9999999</v>
@@ -9926,7 +9926,7 @@
         <v>40596</v>
       </c>
       <c r="J171">
-        <v>197</v>
+        <v>414</v>
       </c>
       <c r="K171">
         <v>9999999</v>
@@ -9982,7 +9982,7 @@
         <v>40596</v>
       </c>
       <c r="J172">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="K172">
         <v>9999999</v>
@@ -10094,7 +10094,7 @@
         <v>40596</v>
       </c>
       <c r="J174">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="K174">
         <v>9999999</v>
@@ -10147,10 +10147,10 @@
         <v>0</v>
       </c>
       <c r="I175">
-        <v>27792</v>
+        <v>28944</v>
       </c>
       <c r="J175">
-        <v>383</v>
+        <v>370</v>
       </c>
       <c r="K175">
         <v>9999999</v>
@@ -10262,7 +10262,7 @@
         <v>29762.5</v>
       </c>
       <c r="J177">
-        <v>6264</v>
+        <v>4200</v>
       </c>
       <c r="K177">
         <v>9999999</v>
@@ -10315,10 +10315,10 @@
         <v>0</v>
       </c>
       <c r="I178">
-        <v>21015.1</v>
+        <v>25267.4</v>
       </c>
       <c r="J178">
-        <v>808</v>
+        <v>439</v>
       </c>
       <c r="K178">
         <v>9999999</v>
@@ -10371,10 +10371,10 @@
         <v>0</v>
       </c>
       <c r="I179">
-        <v>19293</v>
+        <v>23234</v>
       </c>
       <c r="J179">
-        <v>180</v>
+        <v>58</v>
       </c>
       <c r="K179">
         <v>9999999</v>
@@ -10430,7 +10430,7 @@
         <v>45203.6</v>
       </c>
       <c r="J180">
-        <v>152</v>
+        <v>36</v>
       </c>
       <c r="K180">
         <v>9999999</v>
@@ -10486,7 +10486,7 @@
         <v>2739.1</v>
       </c>
       <c r="J181">
-        <v>1199</v>
+        <v>1163</v>
       </c>
       <c r="K181">
         <v>9999999</v>
@@ -10710,7 +10710,7 @@
         <v>5795.5</v>
       </c>
       <c r="J185">
-        <v>2431</v>
+        <v>2422</v>
       </c>
       <c r="K185">
         <v>9999999</v>
@@ -10878,7 +10878,7 @@
         <v>42769.6</v>
       </c>
       <c r="J188">
-        <v>232</v>
+        <v>136</v>
       </c>
       <c r="K188">
         <v>9999999</v>
@@ -10934,7 +10934,7 @@
         <v>15694.1</v>
       </c>
       <c r="J189">
-        <v>792</v>
+        <v>777</v>
       </c>
       <c r="K189">
         <v>9999999</v>
@@ -10990,7 +10990,7 @@
         <v>9161.3</v>
       </c>
       <c r="J190">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="K190">
         <v>9999999</v>
@@ -11046,7 +11046,7 @@
         <v>1329.4</v>
       </c>
       <c r="J191">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="K191">
         <v>9999999</v>
@@ -11155,10 +11155,10 @@
         <v>0</v>
       </c>
       <c r="I193">
-        <v>32095.3</v>
+        <v>38614.1</v>
       </c>
       <c r="J193">
-        <v>366</v>
+        <v>127</v>
       </c>
       <c r="K193">
         <v>9999999</v>
@@ -11774,7 +11774,7 @@
         <v>44957.6</v>
       </c>
       <c r="J204">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="K204">
         <v>9999999</v>
@@ -11827,10 +11827,10 @@
         <v>0</v>
       </c>
       <c r="I205">
-        <v>2376.1</v>
+        <v>2398.5</v>
       </c>
       <c r="J205">
-        <v>137</v>
+        <v>15</v>
       </c>
       <c r="K205">
         <v>9999999</v>
@@ -11886,7 +11886,7 @@
         <v>8637</v>
       </c>
       <c r="J206">
-        <v>2244</v>
+        <v>4139</v>
       </c>
       <c r="K206">
         <v>9999999</v>
@@ -11942,7 +11942,7 @@
         <v>7836.5</v>
       </c>
       <c r="J207">
-        <v>2913</v>
+        <v>2530</v>
       </c>
       <c r="K207">
         <v>9999999</v>
@@ -11995,10 +11995,10 @@
         <v>0</v>
       </c>
       <c r="I208">
-        <v>1589.4</v>
+        <v>1718.9</v>
       </c>
       <c r="J208">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K208">
         <v>9999999</v>
@@ -12051,10 +12051,10 @@
         <v>0</v>
       </c>
       <c r="I209">
-        <v>674.1</v>
+        <v>729</v>
       </c>
       <c r="J209">
-        <v>707</v>
+        <v>792</v>
       </c>
       <c r="K209">
         <v>9999999</v>
@@ -12107,10 +12107,10 @@
         <v>0</v>
       </c>
       <c r="I210">
-        <v>1428.1</v>
+        <v>3732.5</v>
       </c>
       <c r="J210">
-        <v>282</v>
+        <v>252</v>
       </c>
       <c r="K210">
         <v>9999999</v>
@@ -12163,10 +12163,10 @@
         <v>0</v>
       </c>
       <c r="I211">
-        <v>532.3</v>
+        <v>572.5</v>
       </c>
       <c r="J211">
-        <v>415</v>
+        <v>488</v>
       </c>
       <c r="K211">
         <v>9999999</v>
@@ -12275,10 +12275,10 @@
         <v>0</v>
       </c>
       <c r="I213">
-        <v>1333.8</v>
+        <v>1537</v>
       </c>
       <c r="J213">
-        <v>435</v>
+        <v>343</v>
       </c>
       <c r="K213">
         <v>9999999</v>
@@ -12331,10 +12331,10 @@
         <v>0</v>
       </c>
       <c r="I214">
-        <v>676.1</v>
+        <v>815.1</v>
       </c>
       <c r="J214">
-        <v>447</v>
+        <v>300</v>
       </c>
       <c r="K214">
         <v>9999999</v>
@@ -12443,10 +12443,10 @@
         <v>0</v>
       </c>
       <c r="I216">
-        <v>551631.4</v>
+        <v>569518.7</v>
       </c>
       <c r="J216">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K216">
         <v>9999999</v>
@@ -12502,7 +12502,7 @@
         <v>182850</v>
       </c>
       <c r="J217">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K217">
         <v>9999999</v>
@@ -12555,10 +12555,10 @@
         <v>0</v>
       </c>
       <c r="I218">
-        <v>7807.8</v>
+        <v>8480.9</v>
       </c>
       <c r="J218">
-        <v>173</v>
+        <v>144</v>
       </c>
       <c r="K218">
         <v>9999999</v>
@@ -12611,10 +12611,10 @@
         <v>0</v>
       </c>
       <c r="I219">
-        <v>37158.3</v>
+        <v>39015.6</v>
       </c>
       <c r="J219">
-        <v>609</v>
+        <v>952</v>
       </c>
       <c r="K219">
         <v>9999999</v>
@@ -12670,7 +12670,7 @@
         <v>38877.7</v>
       </c>
       <c r="J220">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K220">
         <v>9999999</v>
@@ -12726,7 +12726,7 @@
         <v>20823.2</v>
       </c>
       <c r="J221">
-        <v>0</v>
+        <v>1386</v>
       </c>
       <c r="K221">
         <v>9999999</v>
@@ -12782,7 +12782,7 @@
         <v>13314.8</v>
       </c>
       <c r="J222">
-        <v>1907</v>
+        <v>1623</v>
       </c>
       <c r="K222">
         <v>9999999</v>
@@ -12838,7 +12838,7 @@
         <v>13480.8</v>
       </c>
       <c r="J223">
-        <v>1220</v>
+        <v>2299</v>
       </c>
       <c r="K223">
         <v>9999999</v>
@@ -12894,7 +12894,7 @@
         <v>159629.8</v>
       </c>
       <c r="J224">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="K224">
         <v>9999999</v>
@@ -12947,10 +12947,10 @@
         <v>0</v>
       </c>
       <c r="I225">
-        <v>9913.8</v>
+        <v>10535</v>
       </c>
       <c r="J225">
-        <v>964</v>
+        <v>439</v>
       </c>
       <c r="K225">
         <v>9999999</v>
@@ -13006,7 +13006,7 @@
         <v>165682.4</v>
       </c>
       <c r="J226">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K226">
         <v>9999999</v>
@@ -13062,7 +13062,7 @@
         <v>2806.2</v>
       </c>
       <c r="J227">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="K227">
         <v>9999999</v>
@@ -13115,10 +13115,10 @@
         <v>0</v>
       </c>
       <c r="I228">
-        <v>1357.2</v>
+        <v>1424.4</v>
       </c>
       <c r="J228">
-        <v>710</v>
+        <v>1252</v>
       </c>
       <c r="K228">
         <v>9999999</v>
@@ -13174,7 +13174,7 @@
         <v>12669</v>
       </c>
       <c r="J229">
-        <v>828</v>
+        <v>685</v>
       </c>
       <c r="K229">
         <v>9999999</v>
@@ -13227,7 +13227,7 @@
         <v>0</v>
       </c>
       <c r="I230">
-        <v>20800.3</v>
+        <v>20800.6</v>
       </c>
       <c r="J230">
         <v>0</v>
@@ -13342,7 +13342,7 @@
         <v>8061.9</v>
       </c>
       <c r="J232">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K232">
         <v>9999999</v>
@@ -13398,7 +13398,7 @@
         <v>10701</v>
       </c>
       <c r="J233">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="K233">
         <v>9999999</v>
@@ -13451,10 +13451,10 @@
         <v>0</v>
       </c>
       <c r="I234">
-        <v>6845</v>
+        <v>7186.9</v>
       </c>
       <c r="J234">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="K234">
         <v>9999999</v>
@@ -13510,7 +13510,7 @@
         <v>29724.7</v>
       </c>
       <c r="J235">
-        <v>193</v>
+        <v>166</v>
       </c>
       <c r="K235">
         <v>9999999</v>
@@ -13619,7 +13619,7 @@
         <v>0</v>
       </c>
       <c r="I237">
-        <v>23209.2</v>
+        <v>24879.6</v>
       </c>
       <c r="J237">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="I238">
-        <v>19120.2</v>
+        <v>24019.5</v>
       </c>
       <c r="J238">
-        <v>240</v>
+        <v>156</v>
       </c>
       <c r="K238">
         <v>9999999</v>
@@ -13731,10 +13731,10 @@
         <v>0</v>
       </c>
       <c r="I239">
-        <v>21807.1</v>
+        <v>22892.8</v>
       </c>
       <c r="J239">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="K239">
         <v>9999999</v>
@@ -13787,10 +13787,10 @@
         <v>0</v>
       </c>
       <c r="I240">
-        <v>18671.6</v>
+        <v>22238.4</v>
       </c>
       <c r="J240">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="K240">
         <v>9999999</v>
@@ -13846,7 +13846,7 @@
         <v>28100.94</v>
       </c>
       <c r="J241">
-        <v>2893</v>
+        <v>2134</v>
       </c>
       <c r="K241">
         <v>9999999</v>
@@ -13902,7 +13902,7 @@
         <v>15578.7</v>
       </c>
       <c r="J242">
-        <v>1962</v>
+        <v>1429</v>
       </c>
       <c r="K242">
         <v>9999999</v>
@@ -13955,10 +13955,10 @@
         <v>0</v>
       </c>
       <c r="I243">
-        <v>37826.6</v>
+        <v>50117.9</v>
       </c>
       <c r="J243">
-        <v>61</v>
+        <v>188</v>
       </c>
       <c r="K243">
         <v>9999999</v>
@@ -14011,10 +14011,10 @@
         <v>0</v>
       </c>
       <c r="I244">
-        <v>36022.6</v>
+        <v>44800.7</v>
       </c>
       <c r="J244">
-        <v>245</v>
+        <v>449</v>
       </c>
       <c r="K244">
         <v>9999999</v>
@@ -14070,7 +14070,7 @@
         <v>7979.7</v>
       </c>
       <c r="J245">
-        <v>1031</v>
+        <v>974</v>
       </c>
       <c r="K245">
         <v>9999999</v>
@@ -14126,7 +14126,7 @@
         <v>14594.1</v>
       </c>
       <c r="J246">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K246">
         <v>9999999</v>
@@ -14182,7 +14182,7 @@
         <v>23137.4</v>
       </c>
       <c r="J247">
-        <v>261</v>
+        <v>116</v>
       </c>
       <c r="K247">
         <v>9999999</v>
@@ -14235,10 +14235,10 @@
         <v>0</v>
       </c>
       <c r="I248">
-        <v>2266.9</v>
+        <v>3113.2</v>
       </c>
       <c r="J248">
-        <v>402</v>
+        <v>1086</v>
       </c>
       <c r="K248">
         <v>9999999</v>
@@ -14571,10 +14571,10 @@
         <v>0</v>
       </c>
       <c r="I254">
-        <v>8662.9</v>
+        <v>9095.9</v>
       </c>
       <c r="J254">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="K254">
         <v>9999999</v>
@@ -14686,7 +14686,7 @@
         <v>23953.35</v>
       </c>
       <c r="J256">
-        <v>413</v>
+        <v>223</v>
       </c>
       <c r="K256">
         <v>9999999</v>
@@ -14742,7 +14742,7 @@
         <v>63546.65</v>
       </c>
       <c r="J257">
-        <v>303</v>
+        <v>396</v>
       </c>
       <c r="K257">
         <v>9999999</v>
@@ -14798,7 +14798,7 @@
         <v>9204.2</v>
       </c>
       <c r="J258">
-        <v>1813</v>
+        <v>1517</v>
       </c>
       <c r="K258">
         <v>9999999</v>
@@ -14854,7 +14854,7 @@
         <v>15525</v>
       </c>
       <c r="J259">
-        <v>5852</v>
+        <v>5773</v>
       </c>
       <c r="K259">
         <v>9999999</v>
@@ -14910,7 +14910,7 @@
         <v>52014.5</v>
       </c>
       <c r="J260">
-        <v>110</v>
+        <v>33</v>
       </c>
       <c r="K260">
         <v>9999999</v>
@@ -14963,10 +14963,10 @@
         <v>0</v>
       </c>
       <c r="I261">
-        <v>15870</v>
+        <v>18400</v>
       </c>
       <c r="J261">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K261">
         <v>9999999</v>
@@ -15078,7 +15078,7 @@
         <v>2122891</v>
       </c>
       <c r="J263">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K263">
         <v>9999999</v>
@@ -15190,7 +15190,7 @@
         <v>1322425.7</v>
       </c>
       <c r="J265">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="K265">
         <v>9999999</v>
@@ -15302,7 +15302,7 @@
         <v>2002998</v>
       </c>
       <c r="J267">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K267">
         <v>9999999</v>
@@ -15358,7 +15358,7 @@
         <v>73401.76</v>
       </c>
       <c r="J268">
-        <v>1045</v>
+        <v>836</v>
       </c>
       <c r="K268">
         <v>9999999</v>
@@ -15411,10 +15411,10 @@
         <v>0</v>
       </c>
       <c r="I269">
-        <v>29151</v>
+        <v>29338.9</v>
       </c>
       <c r="J269">
-        <v>1440</v>
+        <v>1433</v>
       </c>
       <c r="K269">
         <v>9999999</v>
@@ -15470,7 +15470,7 @@
         <v>31063.7</v>
       </c>
       <c r="J270">
-        <v>815</v>
+        <v>611</v>
       </c>
       <c r="K270">
         <v>9999999</v>
@@ -15526,7 +15526,7 @@
         <v>33239.6</v>
       </c>
       <c r="J271">
-        <v>1016</v>
+        <v>1327</v>
       </c>
       <c r="K271">
         <v>9999999</v>
@@ -15582,7 +15582,7 @@
         <v>31521.3</v>
       </c>
       <c r="J272">
-        <v>1068</v>
+        <v>851</v>
       </c>
       <c r="K272">
         <v>9999999</v>
@@ -15638,7 +15638,7 @@
         <v>31002.2</v>
       </c>
       <c r="J273">
-        <v>276</v>
+        <v>555</v>
       </c>
       <c r="K273">
         <v>9999999</v>
@@ -15694,7 +15694,7 @@
         <v>13522.7</v>
       </c>
       <c r="J274">
-        <v>995</v>
+        <v>95</v>
       </c>
       <c r="K274">
         <v>9999999</v>
@@ -15747,10 +15747,10 @@
         <v>0</v>
       </c>
       <c r="I275">
-        <v>12351.4</v>
+        <v>13549.5</v>
       </c>
       <c r="J275">
-        <v>3280</v>
+        <v>3116</v>
       </c>
       <c r="K275">
         <v>9999999</v>
@@ -15806,7 +15806,7 @@
         <v>13522.7</v>
       </c>
       <c r="J276">
-        <v>4622</v>
+        <v>2783</v>
       </c>
       <c r="K276">
         <v>9999999</v>
@@ -15918,7 +15918,7 @@
         <v>21658.7</v>
       </c>
       <c r="J278">
-        <v>4920</v>
+        <v>4486</v>
       </c>
       <c r="K278">
         <v>9999999</v>
@@ -15974,7 +15974,7 @@
         <v>11409.7</v>
       </c>
       <c r="J279">
-        <v>7380</v>
+        <v>6550</v>
       </c>
       <c r="K279">
         <v>9999999</v>
@@ -16027,10 +16027,10 @@
         <v>0</v>
       </c>
       <c r="I280">
-        <v>22418.6</v>
+        <v>24593.2</v>
       </c>
       <c r="J280">
-        <v>2021</v>
+        <v>698</v>
       </c>
       <c r="K280">
         <v>9999999</v>
@@ -16086,7 +16086,7 @@
         <v>107204.6</v>
       </c>
       <c r="J281">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="K281">
         <v>9999999</v>
@@ -16142,7 +16142,7 @@
         <v>2648.5</v>
       </c>
       <c r="J282">
-        <v>1134</v>
+        <v>1122</v>
       </c>
       <c r="K282">
         <v>9999999</v>
@@ -16254,7 +16254,7 @@
         <v>41931.9</v>
       </c>
       <c r="J284">
-        <v>435</v>
+        <v>187</v>
       </c>
       <c r="K284">
         <v>9999999</v>
@@ -16307,10 +16307,10 @@
         <v>0</v>
       </c>
       <c r="I285">
-        <v>20270.2</v>
+        <v>20270.4</v>
       </c>
       <c r="J285">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="K285">
         <v>9999999</v>
@@ -16366,7 +16366,7 @@
         <v>4832.3</v>
       </c>
       <c r="J286">
-        <v>325</v>
+        <v>211</v>
       </c>
       <c r="K286">
         <v>9999999</v>
@@ -16422,7 +16422,7 @@
         <v>4832.3</v>
       </c>
       <c r="J287">
-        <v>486</v>
+        <v>338</v>
       </c>
       <c r="K287">
         <v>9999999</v>
@@ -16534,7 +16534,7 @@
         <v>4832.3</v>
       </c>
       <c r="J289">
-        <v>421</v>
+        <v>256</v>
       </c>
       <c r="K289">
         <v>9999999</v>
@@ -16590,7 +16590,7 @@
         <v>4832.3</v>
       </c>
       <c r="J290">
-        <v>550</v>
+        <v>365</v>
       </c>
       <c r="K290">
         <v>9999999</v>
@@ -16646,7 +16646,7 @@
         <v>5535</v>
       </c>
       <c r="J291">
-        <v>296</v>
+        <v>205</v>
       </c>
       <c r="K291">
         <v>9999999</v>
@@ -16758,7 +16758,7 @@
         <v>824847.3</v>
       </c>
       <c r="J293">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="K293">
         <v>9999999</v>
@@ -16811,10 +16811,10 @@
         <v>0</v>
       </c>
       <c r="I294">
-        <v>761673.3</v>
+        <v>796083.4</v>
       </c>
       <c r="J294">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K294">
         <v>9999999</v>
@@ -16867,7 +16867,7 @@
         <v>0</v>
       </c>
       <c r="I295">
-        <v>913686.5</v>
+        <v>944941.9</v>
       </c>
       <c r="J295">
         <v>4</v>
@@ -16926,7 +16926,7 @@
         <v>74425.1</v>
       </c>
       <c r="J296">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="K296">
         <v>9999999</v>
@@ -16982,7 +16982,7 @@
         <v>8306.7</v>
       </c>
       <c r="J297">
-        <v>20503</v>
+        <v>19508</v>
       </c>
       <c r="K297">
         <v>9999999</v>
@@ -17091,10 +17091,10 @@
         <v>0</v>
       </c>
       <c r="I299">
-        <v>89524.6</v>
+        <v>93105.6</v>
       </c>
       <c r="J299">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="K299">
         <v>9999999</v>
@@ -17150,7 +17150,7 @@
         <v>45203.6</v>
       </c>
       <c r="J300">
-        <v>204</v>
+        <v>132</v>
       </c>
       <c r="K300">
         <v>9999999</v>
@@ -17371,10 +17371,10 @@
         <v>0</v>
       </c>
       <c r="I304">
-        <v>70688.2</v>
+        <v>75294</v>
       </c>
       <c r="J304">
-        <v>468</v>
+        <v>180</v>
       </c>
       <c r="K304">
         <v>9999999</v>
@@ -17486,7 +17486,7 @@
         <v>2750.8</v>
       </c>
       <c r="J306">
-        <v>1887</v>
+        <v>1669</v>
       </c>
       <c r="K306">
         <v>9999999</v>
@@ -17654,7 +17654,7 @@
         <v>493282.3</v>
       </c>
       <c r="J309">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="K309">
         <v>9999999</v>
@@ -17710,7 +17710,7 @@
         <v>117657.1</v>
       </c>
       <c r="J310">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="K310">
         <v>9999999</v>
@@ -17766,7 +17766,7 @@
         <v>84804.4</v>
       </c>
       <c r="J311">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="K311">
         <v>9999999</v>
@@ -17822,7 +17822,7 @@
         <v>481566.1</v>
       </c>
       <c r="J312">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K312">
         <v>9999999</v>
@@ -17878,7 +17878,7 @@
         <v>110370.4</v>
       </c>
       <c r="J313">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="K313">
         <v>9999999</v>
@@ -17987,10 +17987,10 @@
         <v>0</v>
       </c>
       <c r="I315">
-        <v>173699.5</v>
+        <v>196939.8</v>
       </c>
       <c r="J315">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K315">
         <v>9999999</v>
@@ -18046,7 +18046,7 @@
         <v>346227.5</v>
       </c>
       <c r="J316">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="K316">
         <v>9999999</v>
@@ -18155,10 +18155,10 @@
         <v>0</v>
       </c>
       <c r="I318">
-        <v>22418.6</v>
+        <v>24593.2</v>
       </c>
       <c r="J318">
-        <v>1334</v>
+        <v>1285</v>
       </c>
       <c r="K318">
         <v>9999999</v>
@@ -18214,7 +18214,7 @@
         <v>24534.5</v>
       </c>
       <c r="J319">
-        <v>2623</v>
+        <v>2293</v>
       </c>
       <c r="K319">
         <v>9999999</v>
@@ -18267,7 +18267,7 @@
         <v>0</v>
       </c>
       <c r="I320">
-        <v>12696.69</v>
+        <v>12699.31</v>
       </c>
       <c r="J320">
         <v>0</v>
@@ -18323,10 +18323,10 @@
         <v>0</v>
       </c>
       <c r="I321">
-        <v>37847.69</v>
+        <v>42514.09</v>
       </c>
       <c r="J321">
-        <v>692</v>
+        <v>201</v>
       </c>
       <c r="K321">
         <v>9999999</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="I322">
-        <v>64559.7</v>
+        <v>70922.6</v>
       </c>
       <c r="J322">
-        <v>2527</v>
+        <v>1510</v>
       </c>
       <c r="K322">
         <v>9999999</v>
@@ -18494,7 +18494,7 @@
         <v>177120</v>
       </c>
       <c r="J324">
-        <v>1737</v>
+        <v>1667</v>
       </c>
       <c r="K324">
         <v>9999999</v>
@@ -18550,7 +18550,7 @@
         <v>36288.1</v>
       </c>
       <c r="J325">
-        <v>3875</v>
+        <v>3781</v>
       </c>
       <c r="K325">
         <v>9999999</v>
@@ -18659,10 +18659,10 @@
         <v>0</v>
       </c>
       <c r="I327">
-        <v>10412</v>
+        <v>10701</v>
       </c>
       <c r="J327">
-        <v>1967</v>
+        <v>997</v>
       </c>
       <c r="K327">
         <v>9999999</v>
@@ -19222,7 +19222,7 @@
         <v>29268.8</v>
       </c>
       <c r="J337">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="K337">
         <v>9999999</v>
@@ -19278,7 +19278,7 @@
         <v>29268.8</v>
       </c>
       <c r="J338">
-        <v>337</v>
+        <v>323</v>
       </c>
       <c r="K338">
         <v>9999999</v>
@@ -19334,7 +19334,7 @@
         <v>29268.8</v>
       </c>
       <c r="J339">
-        <v>926</v>
+        <v>895</v>
       </c>
       <c r="K339">
         <v>9999999</v>
@@ -19390,7 +19390,7 @@
         <v>29268.8</v>
       </c>
       <c r="J340">
-        <v>359</v>
+        <v>321</v>
       </c>
       <c r="K340">
         <v>9999999</v>
@@ -19446,7 +19446,7 @@
         <v>29268.8</v>
       </c>
       <c r="J341">
-        <v>596</v>
+        <v>545</v>
       </c>
       <c r="K341">
         <v>9999999</v>
@@ -19502,7 +19502,7 @@
         <v>29268.8</v>
       </c>
       <c r="J342">
-        <v>142</v>
+        <v>90</v>
       </c>
       <c r="K342">
         <v>9999999</v>
@@ -19558,7 +19558,7 @@
         <v>29268.8</v>
       </c>
       <c r="J343">
-        <v>87</v>
+        <v>49</v>
       </c>
       <c r="K343">
         <v>9999999</v>
@@ -19726,7 +19726,7 @@
         <v>13422.4</v>
       </c>
       <c r="J346">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="K346">
         <v>9999999</v>
@@ -20230,7 +20230,7 @@
         <v>90850</v>
       </c>
       <c r="J355">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="K355">
         <v>9999999</v>
@@ -20286,7 +20286,7 @@
         <v>276000</v>
       </c>
       <c r="J356">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="K356">
         <v>9999999</v>
@@ -20398,7 +20398,7 @@
         <v>230000</v>
       </c>
       <c r="J358">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K358">
         <v>9999999</v>
@@ -20622,7 +20622,7 @@
         <v>30584.5</v>
       </c>
       <c r="J362">
-        <v>2610</v>
+        <v>2573</v>
       </c>
       <c r="K362">
         <v>9999999</v>
@@ -20846,7 +20846,7 @@
         <v>4584.1</v>
       </c>
       <c r="J366">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="K366">
         <v>9999999</v>
@@ -20899,10 +20899,10 @@
         <v>0</v>
       </c>
       <c r="I367">
-        <v>19690</v>
+        <v>21325.8</v>
       </c>
       <c r="J367">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="K367">
         <v>9999999</v>
@@ -21406,7 +21406,7 @@
         <v>270616.5</v>
       </c>
       <c r="J376">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K376">
         <v>9999999</v>
@@ -21462,7 +21462,7 @@
         <v>43513.7</v>
       </c>
       <c r="J377">
-        <v>731</v>
+        <v>1378</v>
       </c>
       <c r="K377">
         <v>9999999</v>
@@ -21518,7 +21518,7 @@
         <v>84258.5</v>
       </c>
       <c r="J378">
-        <v>1452</v>
+        <v>668</v>
       </c>
       <c r="K378">
         <v>9999999</v>
@@ -21686,7 +21686,7 @@
         <v>28233</v>
       </c>
       <c r="J381">
-        <v>1452</v>
+        <v>1094</v>
       </c>
       <c r="K381">
         <v>9999999</v>
@@ -21742,7 +21742,7 @@
         <v>73701.35</v>
       </c>
       <c r="J382">
-        <v>1450</v>
+        <v>1092</v>
       </c>
       <c r="K382">
         <v>9999999</v>
@@ -21798,7 +21798,7 @@
         <v>29268.8</v>
       </c>
       <c r="J383">
-        <v>682</v>
+        <v>637</v>
       </c>
       <c r="K383">
         <v>9999999</v>
@@ -21851,10 +21851,10 @@
         <v>0</v>
       </c>
       <c r="I384">
-        <v>216598.8</v>
+        <v>222984.7</v>
       </c>
       <c r="J384">
-        <v>176</v>
+        <v>148</v>
       </c>
       <c r="K384">
         <v>9999999</v>
@@ -22022,7 +22022,7 @@
         <v>14020.2</v>
       </c>
       <c r="J387">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="K387">
         <v>9999999</v>
@@ -22078,7 +22078,7 @@
         <v>0.1</v>
       </c>
       <c r="J388">
-        <v>141</v>
+        <v>110</v>
       </c>
       <c r="K388">
         <v>9999999</v>
@@ -22134,7 +22134,7 @@
         <v>971005.2</v>
       </c>
       <c r="J389">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K389">
         <v>9999999</v>
@@ -22187,10 +22187,10 @@
         <v>0</v>
       </c>
       <c r="I390">
-        <v>21955.2</v>
+        <v>24879.6</v>
       </c>
       <c r="J390">
-        <v>2476</v>
+        <v>5119</v>
       </c>
       <c r="K390">
         <v>9999999</v>
@@ -22411,10 +22411,10 @@
         <v>0</v>
       </c>
       <c r="I394">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="J394">
-        <v>319</v>
+        <v>138</v>
       </c>
       <c r="K394">
         <v>9999999</v>
@@ -22470,7 +22470,7 @@
         <v>88328.8</v>
       </c>
       <c r="J395">
-        <v>1167</v>
+        <v>721</v>
       </c>
       <c r="K395">
         <v>9999999</v>
@@ -22526,7 +22526,7 @@
         <v>41255.9</v>
       </c>
       <c r="J396">
-        <v>4618</v>
+        <v>4409</v>
       </c>
       <c r="K396">
         <v>9999999</v>
@@ -22582,7 +22582,7 @@
         <v>0.01</v>
       </c>
       <c r="J397">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K397">
         <v>9999999</v>
@@ -22638,7 +22638,7 @@
         <v>87713.6</v>
       </c>
       <c r="J398">
-        <v>4405</v>
+        <v>0</v>
       </c>
       <c r="K398">
         <v>9999999</v>
@@ -22667,10 +22667,10 @@
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>010- PRODUCTOS PROMOCIONALES</v>
+        <v xml:space="preserve">I12- PRODUCTOS DE LIMPIEZA </v>
       </c>
       <c r="B399" t="str">
-        <v>6003306</v>
+        <v>6002552</v>
       </c>
       <c r="C399">
         <v>0</v>
@@ -22679,22 +22679,22 @@
         <v>2027;2027</v>
       </c>
       <c r="E399" t="str">
-        <v xml:space="preserve">EXHIBIDOR GRIDO TOY 2 EDICION X UN      </v>
+        <v xml:space="preserve">BASURERO BASCULANTE 60L                 </v>
       </c>
       <c r="F399">
-        <v>0.5</v>
+        <v>0.66667</v>
       </c>
       <c r="G399">
-        <v>1</v>
+        <v>1.76</v>
       </c>
       <c r="H399">
         <v>0</v>
       </c>
       <c r="I399">
-        <v>7367.7</v>
+        <v>7539.4</v>
       </c>
       <c r="J399">
-        <v>448</v>
+        <v>63</v>
       </c>
       <c r="K399">
         <v>9999999</v>
@@ -22726,7 +22726,7 @@
         <v>010- PRODUCTOS PROMOCIONALES</v>
       </c>
       <c r="B400" t="str">
-        <v>6003001</v>
+        <v>6003306</v>
       </c>
       <c r="C400">
         <v>0</v>
@@ -22735,10 +22735,10 @@
         <v>2027;2027</v>
       </c>
       <c r="E400" t="str">
-        <v>GR TOY WILD MONSTER_RAINBOW PONIE X 80UN</v>
+        <v xml:space="preserve">EXHIBIDOR GRIDO TOY 2 EDICION X UN      </v>
       </c>
       <c r="F400">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="G400">
         <v>1</v>
@@ -22747,10 +22747,10 @@
         <v>0</v>
       </c>
       <c r="I400">
-        <v>73185</v>
+        <v>7367.7</v>
       </c>
       <c r="J400">
-        <v>0</v>
+        <v>424</v>
       </c>
       <c r="K400">
         <v>9999999</v>
@@ -22779,10 +22779,10 @@
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>I02-GRIDO CAFE</v>
+        <v>010- PRODUCTOS PROMOCIONALES</v>
       </c>
       <c r="B401" t="str">
-        <v>6000700</v>
+        <v>6003001</v>
       </c>
       <c r="C401">
         <v>0</v>
@@ -22791,22 +22791,22 @@
         <v>2027;2027</v>
       </c>
       <c r="E401" t="str">
-        <v xml:space="preserve">TAPA VASO POLIPAPEL G.CAFE 12OZ X 2000  </v>
+        <v>GR TOY WILD MONSTER_RAINBOW PONIE X 80UN</v>
       </c>
       <c r="F401">
-        <v>5.556</v>
+        <v>1.25</v>
       </c>
       <c r="G401">
-        <v>4.96</v>
+        <v>1</v>
       </c>
       <c r="H401">
         <v>0</v>
       </c>
       <c r="I401">
-        <v>49270.5</v>
+        <v>73185</v>
       </c>
       <c r="J401">
-        <v>346</v>
+        <v>0</v>
       </c>
       <c r="K401">
         <v>9999999</v>
@@ -22835,10 +22835,10 @@
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>I01- GRIDO MARKET</v>
+        <v>I02-GRIDO CAFE</v>
       </c>
       <c r="B402" t="str">
-        <v>6000701</v>
+        <v>6000700</v>
       </c>
       <c r="C402">
         <v>0</v>
@@ -22847,22 +22847,22 @@
         <v>2027;2027</v>
       </c>
       <c r="E402" t="str">
-        <v xml:space="preserve">COLLARIN ESPAÑOL G.CAFE 2 COL X 1000 UN </v>
+        <v xml:space="preserve">TAPA VASO POLIPAPEL G.CAFE 12OZ X 2000  </v>
       </c>
       <c r="F402">
-        <v>2.5</v>
+        <v>5.556</v>
       </c>
       <c r="G402">
-        <v>3.84</v>
+        <v>4.96</v>
       </c>
       <c r="H402">
         <v>0</v>
       </c>
       <c r="I402">
-        <v>33747.7</v>
+        <v>49270.5</v>
       </c>
       <c r="J402">
-        <v>115</v>
+        <v>315</v>
       </c>
       <c r="K402">
         <v>9999999</v>
@@ -22891,10 +22891,10 @@
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>I02-GRIDO CAFE</v>
+        <v>I01- GRIDO MARKET</v>
       </c>
       <c r="B403" t="str">
-        <v>6000698</v>
+        <v>6000701</v>
       </c>
       <c r="C403">
         <v>0</v>
@@ -22903,22 +22903,22 @@
         <v>2027;2027</v>
       </c>
       <c r="E403" t="str">
-        <v>TAPA VASO POLIPAPEL G.CAFE 8OZ X2000 Un.</v>
+        <v xml:space="preserve">COLLARIN ESPAÑOL G.CAFE 2 COL X 1000 UN </v>
       </c>
       <c r="F403">
-        <v>5.556</v>
+        <v>2.5</v>
       </c>
       <c r="G403">
-        <v>3.86</v>
+        <v>3.84</v>
       </c>
       <c r="H403">
         <v>0</v>
       </c>
       <c r="I403">
-        <v>48024.2</v>
+        <v>33747.7</v>
       </c>
       <c r="J403">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="K403">
         <v>9999999</v>
@@ -22950,7 +22950,7 @@
         <v>I02-GRIDO CAFE</v>
       </c>
       <c r="B404" t="str">
-        <v>6000695</v>
+        <v>6000698</v>
       </c>
       <c r="C404">
         <v>0</v>
@@ -22959,22 +22959,22 @@
         <v>2027;2027</v>
       </c>
       <c r="E404" t="str">
-        <v xml:space="preserve">REMOVEDOR CAFE  X 1000 Un.              </v>
+        <v>TAPA VASO POLIPAPEL G.CAFE 8OZ X2000 Un.</v>
       </c>
       <c r="F404">
-        <v>0.154</v>
+        <v>5.556</v>
       </c>
       <c r="G404">
-        <v>1.05</v>
+        <v>3.86</v>
       </c>
       <c r="H404">
         <v>0</v>
       </c>
       <c r="I404">
-        <v>33267.2</v>
+        <v>48024.2</v>
       </c>
       <c r="J404">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="K404">
         <v>9999999</v>
@@ -23003,10 +23003,10 @@
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>I03- CUCURUCHOS , CONOS Y VASOS DE  PASTA</v>
+        <v>I02-GRIDO CAFE</v>
       </c>
       <c r="B405" t="str">
-        <v>6001619</v>
+        <v>6000695</v>
       </c>
       <c r="C405">
         <v>0</v>
@@ -23015,22 +23015,22 @@
         <v>2027;2027</v>
       </c>
       <c r="E405" t="str">
-        <v xml:space="preserve">CUCURUCHON BIOCUPS X 240 UN             </v>
+        <v xml:space="preserve">REMOVEDOR CAFE  X 1000 Un.              </v>
       </c>
       <c r="F405">
-        <v>2.777</v>
+        <v>0.154</v>
       </c>
       <c r="G405">
-        <v>3.6</v>
+        <v>1.05</v>
       </c>
       <c r="H405">
         <v>0</v>
       </c>
       <c r="I405">
-        <v>21423.7</v>
+        <v>33267.2</v>
       </c>
       <c r="J405">
-        <v>14984</v>
+        <v>23</v>
       </c>
       <c r="K405">
         <v>9999999</v>
@@ -23059,10 +23059,10 @@
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>010- PRODUCTOS PROMOCIONALES</v>
+        <v>I03- CUCURUCHOS , CONOS Y VASOS DE  PASTA</v>
       </c>
       <c r="B406" t="str">
-        <v>7101030</v>
+        <v>6001619</v>
       </c>
       <c r="C406">
         <v>0</v>
@@ -23071,16 +23071,22 @@
         <v>2027;2027</v>
       </c>
       <c r="E406" t="str">
-        <v xml:space="preserve">GORRA CELESTE Y BLANCA MUNDIAL MKT      </v>
+        <v xml:space="preserve">CUCURUCHON BIOCUPS X 240 UN             </v>
+      </c>
+      <c r="F406">
+        <v>2.777</v>
+      </c>
+      <c r="G406">
+        <v>3.6</v>
       </c>
       <c r="H406">
         <v>0</v>
       </c>
       <c r="I406">
-        <v>0.01</v>
+        <v>21895</v>
       </c>
       <c r="J406">
-        <v>6020</v>
+        <v>10824</v>
       </c>
       <c r="K406">
         <v>9999999</v>
@@ -23112,7 +23118,7 @@
         <v>010- PRODUCTOS PROMOCIONALES</v>
       </c>
       <c r="B407" t="str">
-        <v>7100069</v>
+        <v>7101030</v>
       </c>
       <c r="C407">
         <v>0</v>
@@ -23121,22 +23127,16 @@
         <v>2027;2027</v>
       </c>
       <c r="E407" t="str">
-        <v xml:space="preserve">VINILO PARA KIT PROMOCIONAL             </v>
-      </c>
-      <c r="F407">
-        <v>0.2</v>
-      </c>
-      <c r="G407">
-        <v>2</v>
+        <v xml:space="preserve">GORRA CELESTE Y BLANCA MUNDIAL MKT      </v>
       </c>
       <c r="H407">
         <v>0</v>
       </c>
       <c r="I407">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="J407">
-        <v>1035</v>
+        <v>2191</v>
       </c>
       <c r="K407">
         <v>9999999</v>
@@ -23192,7 +23192,7 @@
         <v>23734.1</v>
       </c>
       <c r="J408">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K408">
         <v>9999999</v>
@@ -23525,7 +23525,7 @@
         <v>0</v>
       </c>
       <c r="I414">
-        <v>21480</v>
+        <v>27810</v>
       </c>
       <c r="J414">
         <v>0</v>
@@ -23973,7 +23973,7 @@
         <v>0</v>
       </c>
       <c r="I422">
-        <v>27792</v>
+        <v>28944</v>
       </c>
       <c r="J422">
         <v>0</v>
@@ -24253,7 +24253,7 @@
         <v>0</v>
       </c>
       <c r="I427">
-        <v>2376.1</v>
+        <v>2398.5</v>
       </c>
       <c r="J427">
         <v>0</v>
@@ -24421,7 +24421,7 @@
         <v>0</v>
       </c>
       <c r="I430">
-        <v>1589.4</v>
+        <v>1718.9</v>
       </c>
       <c r="J430">
         <v>0</v>
@@ -24533,7 +24533,7 @@
         <v>0</v>
       </c>
       <c r="I432">
-        <v>674.1</v>
+        <v>729</v>
       </c>
       <c r="J432">
         <v>0</v>
@@ -24589,7 +24589,7 @@
         <v>0</v>
       </c>
       <c r="I433">
-        <v>1428.1</v>
+        <v>3732.5</v>
       </c>
       <c r="J433">
         <v>0</v>
@@ -24645,7 +24645,7 @@
         <v>0</v>
       </c>
       <c r="I434">
-        <v>532.3</v>
+        <v>572.5</v>
       </c>
       <c r="J434">
         <v>0</v>
@@ -24757,7 +24757,7 @@
         <v>0</v>
       </c>
       <c r="I436">
-        <v>1333.8</v>
+        <v>1537</v>
       </c>
       <c r="J436">
         <v>0</v>
@@ -24813,7 +24813,7 @@
         <v>0</v>
       </c>
       <c r="I437">
-        <v>676.1</v>
+        <v>815.1</v>
       </c>
       <c r="J437">
         <v>0</v>
@@ -25093,7 +25093,7 @@
         <v>0</v>
       </c>
       <c r="I442">
-        <v>9913.8</v>
+        <v>10535</v>
       </c>
       <c r="J442">
         <v>0</v>
@@ -25149,7 +25149,7 @@
         <v>0</v>
       </c>
       <c r="I443">
-        <v>1357.2</v>
+        <v>1424.4</v>
       </c>
       <c r="J443">
         <v>0</v>
@@ -25317,7 +25317,7 @@
         <v>0</v>
       </c>
       <c r="I446">
-        <v>23209.2</v>
+        <v>24879.6</v>
       </c>
       <c r="J446">
         <v>0</v>
@@ -25485,7 +25485,7 @@
         <v>0</v>
       </c>
       <c r="I449">
-        <v>37826.6</v>
+        <v>50117.9</v>
       </c>
       <c r="J449">
         <v>0</v>
@@ -25653,7 +25653,7 @@
         <v>0</v>
       </c>
       <c r="I452">
-        <v>2266.9</v>
+        <v>3113.2</v>
       </c>
       <c r="J452">
         <v>0</v>
@@ -25989,7 +25989,7 @@
         <v>0</v>
       </c>
       <c r="I458">
-        <v>29151</v>
+        <v>29338.9</v>
       </c>
       <c r="J458">
         <v>0</v>
@@ -26325,7 +26325,7 @@
         <v>0</v>
       </c>
       <c r="I464">
-        <v>12351.4</v>
+        <v>13549.5</v>
       </c>
       <c r="J464">
         <v>0</v>
@@ -26605,7 +26605,7 @@
         <v>0</v>
       </c>
       <c r="I469">
-        <v>22418.6</v>
+        <v>24593.2</v>
       </c>
       <c r="J469">
         <v>0</v>
@@ -26885,7 +26885,7 @@
         <v>0</v>
       </c>
       <c r="I474">
-        <v>22418.6</v>
+        <v>24593.2</v>
       </c>
       <c r="J474">
         <v>0</v>
@@ -26941,7 +26941,7 @@
         <v>0</v>
       </c>
       <c r="I475">
-        <v>64559.7</v>
+        <v>70922.6</v>
       </c>
       <c r="J475">
         <v>0</v>
@@ -27109,7 +27109,7 @@
         <v>0</v>
       </c>
       <c r="I478">
-        <v>21423.7</v>
+        <v>21895</v>
       </c>
       <c r="J478">
         <v>0</v>
